--- a/output/details/2026-05-19/preprocessed_data.xlsx
+++ b/output/details/2026-05-19/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46161</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1116866681379777</v>
+        <v>-0.1143567231796103</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1598506854571904</v>
+        <v>-0.1395477702843328</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1596291748748966</v>
+        <v>-0.1392734070087169</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1238969382032208</v>
+        <v>0.001656890520929152</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001700784709498776</v>
+        <v>0.001698706790600567</v>
       </c>
       <c r="G2" t="n">
-        <v>1.903481114216898</v>
+        <v>2.468543913838753</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4444593000560977</v>
+        <v>-0.2670566469627061</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
